--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -415,30 +415,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ffdjjfdj</v>
+        <v>sdfg</v>
       </c>
       <c r="B2">
-        <v>377568</v>
+        <v>54</v>
       </c>
       <c r="C2" t="str">
         <v>Salary</v>
       </c>
       <c r="D2" t="str">
-        <v>5/5/2026</v>
+        <v>8/5/2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>dsffadg</v>
+        <v>sdfg</v>
       </c>
       <c r="B3">
-        <v>36546547</v>
+        <v>345</v>
       </c>
       <c r="C3" t="str">
         <v>Food</v>
       </c>
       <c r="D3" t="str">
-        <v>5/5/2026</v>
+        <v>8/5/2026</v>
       </c>
     </row>
   </sheetData>
